--- a/Budweg/BD_Projekt/Følgeseddel.xlsx
+++ b/Budweg/BD_Projekt/Følgeseddel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MPH\Programmering\2.Semster\Budweg\BD_Projekt\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MPH\Programmering\2.Semster\Budweg_TeamB2\Budweg\BD_Projekt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8CAE4F5-E89E-4623-A3E0-CB6C051285BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81617E2A-5F36-445B-A23F-CF03A8466988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3612" yWindow="3540" windowWidth="17280" windowHeight="9420" xr2:uid="{B3123204-15E3-4ECA-871F-AFC3B18C35E5}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9420" xr2:uid="{B3123204-15E3-4ECA-871F-AFC3B18C35E5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,23 +36,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="9">
   <si>
     <t>station</t>
   </si>
   <si>
-    <t>Montage</t>
-  </si>
-  <si>
-    <t>Rengøring</t>
-  </si>
-  <si>
-    <t>Pakkeri</t>
-  </si>
-  <si>
-    <t>Lager</t>
-  </si>
-  <si>
     <t>WorkorderID</t>
   </si>
   <si>
@@ -69,6 +57,12 @@
   </si>
   <si>
     <t>intake_backwards</t>
+  </si>
+  <si>
+    <t>Følgeselled nr.</t>
+  </si>
+  <si>
+    <t>D</t>
   </si>
 </sst>
 </file>
@@ -470,154 +464,198 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAEFEB1E-76B4-481E-A02F-1A2466C56AD7}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="12.88671875" customWidth="1"/>
-    <col min="3" max="3" width="11.88671875" customWidth="1"/>
-    <col min="4" max="4" width="15.109375" customWidth="1"/>
-    <col min="5" max="5" width="18.88671875" customWidth="1"/>
-    <col min="6" max="6" width="14.6640625" customWidth="1"/>
-    <col min="7" max="7" width="17" customWidth="1"/>
+    <col min="1" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="12.88671875" customWidth="1"/>
+    <col min="4" max="4" width="11.88671875" customWidth="1"/>
+    <col min="5" max="5" width="15.109375" customWidth="1"/>
+    <col min="6" max="6" width="18.88671875" customWidth="1"/>
+    <col min="7" max="7" width="14.6640625" customWidth="1"/>
+    <col min="8" max="8" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>7</v>
+      <c r="H2" s="1">
+        <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1">
-        <v>30</v>
-      </c>
-      <c r="C2" s="1">
-        <v>0</v>
-      </c>
-      <c r="D2" s="1">
-        <v>30</v>
-      </c>
-      <c r="E2" s="1">
-        <v>0</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="C3" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D3" s="1">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E3" s="1">
-        <v>15</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="1">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="F3" s="1">
+        <v>1</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C4" s="1">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="1">
-        <v>7</v>
-      </c>
-      <c r="E4" s="1">
-        <v>3</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="1">
-        <v>4</v>
+      <c r="H4" s="1">
+        <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C5" s="1">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D5" s="1">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G5" s="1">
-        <v>5</v>
+      <c r="F5" s="1">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="1">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C6" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" s="1">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E6" s="1">
-        <v>0</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G6" s="1">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
